--- a/utilities/genetic_diversity/genetic_diversity_r/models_summary_final.xlsx
+++ b/utilities/genetic_diversity/genetic_diversity_r/models_summary_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arimaite/Documents/GitHub/RSV-wastewater-2024-2025/utilities/genetic_diversity/genetic_diversity_r/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E0C1A3-EBDF-324E-96A2-6CD997BBC02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349D871C-32B5-6A41-9891-0604EF8BA4FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16300" xr2:uid="{4E21B9EB-94B6-5B47-B9B2-DB4ACE51F718}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16280" xr2:uid="{4E21B9EB-94B6-5B47-B9B2-DB4ACE51F718}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>Random effect</t>
   </si>
   <si>
-    <t>Subtype, log(mean coverage)</t>
-  </si>
-  <si>
     <t>Diversity metrics (response variables)</t>
   </si>
   <si>
@@ -68,9 +65,6 @@
     <t>F vs G, RSV-B</t>
   </si>
   <si>
-    <t>Gene (F/G), log(mean coverage)</t>
-  </si>
-  <si>
     <t>Nucleotide diversity</t>
   </si>
   <si>
@@ -84,6 +78,12 @@
   </si>
   <si>
     <t>RSV-A vs RSV-B, G gene</t>
+  </si>
+  <si>
+    <t>Subtype, log(mean coverage), log(mean coverage)^2</t>
+  </si>
+  <si>
+    <t>Gene (F/G), log(mean coverage), log(mean coverage)^2</t>
   </si>
 </sst>
 </file>
@@ -132,7 +132,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -361,24 +361,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -409,6 +426,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -747,211 +782,211 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="38.83203125" customWidth="1"/>
-    <col min="4" max="4" width="19.1640625" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
+    <col min="4" max="4" width="32.5" customWidth="1"/>
     <col min="5" max="5" width="16.6640625" customWidth="1"/>
     <col min="6" max="6" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="23" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17"/>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-    </row>
-    <row r="2" spans="1:8" ht="23" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="17"/>
-      <c r="B2" s="1" t="s">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" ht="41" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="12"/>
+      <c r="B2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+    </row>
+    <row r="3" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="12"/>
+      <c r="B3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-    </row>
-    <row r="3" spans="1:8" ht="40" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="6" t="s">
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+    </row>
+    <row r="4" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12"/>
+      <c r="B4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+    </row>
+    <row r="5" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12"/>
+      <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="C5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+    </row>
+    <row r="6" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12"/>
+      <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-    </row>
-    <row r="4" spans="1:8" ht="40" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="12" t="s">
+      <c r="C6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-    </row>
-    <row r="5" spans="1:8" ht="40" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="10" t="s">
+      <c r="F6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+    </row>
+    <row r="7" spans="1:8" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="12" t="s">
+      <c r="E7" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-    </row>
-    <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-    </row>
-    <row r="7" spans="1:8" ht="61" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="17"/>
-      <c r="B7" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
+      <c r="F7" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
     </row>
     <row r="8" spans="1:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
     </row>
     <row r="9" spans="1:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
     </row>
     <row r="10" spans="1:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
     </row>
     <row r="12" spans="1:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
     </row>
     <row r="13" spans="1:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
     </row>
     <row r="14" spans="1:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
